--- a/data/spain/p4_modeling/2024-10-13/df_iteration_train.xlsx
+++ b/data/spain/p4_modeling/2024-10-13/df_iteration_train.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R557"/>
+  <dimension ref="A1:R629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38906,6 +38906,4976 @@
         <v>5</v>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>591</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>3</v>
+      </c>
+      <c r="D558" t="b">
+        <v>0</v>
+      </c>
+      <c r="E558" t="b">
+        <v>1</v>
+      </c>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H558" t="n">
+        <v>10</v>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L558" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M558" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>(741, 35)</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>(154, 35)</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>(123, 35)</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R558" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>592</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>3</v>
+      </c>
+      <c r="D559" t="b">
+        <v>0</v>
+      </c>
+      <c r="E559" t="b">
+        <v>1</v>
+      </c>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H559" t="n">
+        <v>10</v>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L559" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M559" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>(2268, 35)</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>(459, 35)</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>(367, 35)</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R559" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>593</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>3</v>
+      </c>
+      <c r="D560" t="b">
+        <v>0</v>
+      </c>
+      <c r="E560" t="b">
+        <v>1</v>
+      </c>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H560" t="n">
+        <v>10</v>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L560" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M560" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>(1320, 24)</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>(260, 24)</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>(208, 24)</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R560" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>594</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>3</v>
+      </c>
+      <c r="D561" t="b">
+        <v>0</v>
+      </c>
+      <c r="E561" t="b">
+        <v>1</v>
+      </c>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H561" t="n">
+        <v>10</v>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L561" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M561" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>(3267, 24)</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>(650, 24)</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>(520, 24)</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R561" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>595</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>3</v>
+      </c>
+      <c r="D562" t="b">
+        <v>0</v>
+      </c>
+      <c r="E562" t="b">
+        <v>1</v>
+      </c>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H562" t="n">
+        <v>10</v>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L562" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M562" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>(2448, 12)</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>(492, 12)</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>(394, 12)</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R562" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>596</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>3</v>
+      </c>
+      <c r="D563" t="b">
+        <v>0</v>
+      </c>
+      <c r="E563" t="b">
+        <v>1</v>
+      </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H563" t="n">
+        <v>10</v>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L563" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M563" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>(3714, 12)</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>(721, 12)</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>(577, 12)</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R563" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>597</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>3</v>
+      </c>
+      <c r="D564" t="b">
+        <v>0</v>
+      </c>
+      <c r="E564" t="b">
+        <v>0</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G564" t="inlineStr"/>
+      <c r="H564" t="n">
+        <v>3</v>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L564" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M564" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>(462, 46)</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>(102, 46)</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>(82, 46)</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R564" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>598</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>3</v>
+      </c>
+      <c r="D565" t="b">
+        <v>0</v>
+      </c>
+      <c r="E565" t="b">
+        <v>0</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="n">
+        <v>3</v>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L565" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M565" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>(1704, 46)</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>(326, 46)</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>(260, 46)</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R565" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>599</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>3</v>
+      </c>
+      <c r="D566" t="b">
+        <v>0</v>
+      </c>
+      <c r="E566" t="b">
+        <v>0</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G566" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H566" t="n">
+        <v>3</v>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L566" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M566" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>(501, 34)</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>(102, 34)</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>(82, 34)</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R566" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>600</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>3</v>
+      </c>
+      <c r="D567" t="b">
+        <v>0</v>
+      </c>
+      <c r="E567" t="b">
+        <v>0</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G567" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H567" t="n">
+        <v>3</v>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L567" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M567" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>(1680, 34)</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>(326, 34)</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>(261, 34)</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R567" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>601</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>3</v>
+      </c>
+      <c r="D568" t="b">
+        <v>0</v>
+      </c>
+      <c r="E568" t="b">
+        <v>0</v>
+      </c>
+      <c r="F568" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G568" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H568" t="n">
+        <v>3</v>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L568" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M568" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>(654, 23)</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>(130, 23)</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>(104, 23)</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R568" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>602</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>3</v>
+      </c>
+      <c r="D569" t="b">
+        <v>0</v>
+      </c>
+      <c r="E569" t="b">
+        <v>0</v>
+      </c>
+      <c r="F569" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G569" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H569" t="n">
+        <v>3</v>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L569" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M569" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>(1659, 23)</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>(326, 23)</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>(261, 23)</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R569" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>603</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>3</v>
+      </c>
+      <c r="D570" t="b">
+        <v>0</v>
+      </c>
+      <c r="E570" t="b">
+        <v>0</v>
+      </c>
+      <c r="F570" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G570" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H570" t="n">
+        <v>3</v>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L570" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M570" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>(912, 12)</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>(186, 12)</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>(149, 12)</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R570" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>604</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>3</v>
+      </c>
+      <c r="D571" t="b">
+        <v>0</v>
+      </c>
+      <c r="E571" t="b">
+        <v>0</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G571" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H571" t="n">
+        <v>3</v>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L571" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M571" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>(1680, 12)</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>(327, 12)</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>(261, 12)</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R571" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>606</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>3</v>
+      </c>
+      <c r="D572" t="b">
+        <v>0</v>
+      </c>
+      <c r="E572" t="b">
+        <v>0</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G572" t="inlineStr"/>
+      <c r="H572" t="n">
+        <v>3</v>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L572" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M572" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>(1323, 75)</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>(264, 75)</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>(211, 75)</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R572" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>608</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>3</v>
+      </c>
+      <c r="D573" t="b">
+        <v>0</v>
+      </c>
+      <c r="E573" t="b">
+        <v>0</v>
+      </c>
+      <c r="F573" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G573" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H573" t="n">
+        <v>3</v>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L573" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M573" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>(1716, 56)</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>(328, 56)</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>(262, 56)</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R573" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>609</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>3</v>
+      </c>
+      <c r="D574" t="b">
+        <v>0</v>
+      </c>
+      <c r="E574" t="b">
+        <v>0</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G574" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H574" t="n">
+        <v>3</v>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L574" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M574" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>(507, 38)</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>(103, 38)</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>(83, 38)</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>['id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R574" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>610</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>3</v>
+      </c>
+      <c r="D575" t="b">
+        <v>0</v>
+      </c>
+      <c r="E575" t="b">
+        <v>0</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G575" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H575" t="n">
+        <v>3</v>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L575" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M575" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>(1692, 38)</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>(329, 38)</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>(263, 38)</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>['id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R575" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>611</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>3</v>
+      </c>
+      <c r="D576" t="b">
+        <v>0</v>
+      </c>
+      <c r="E576" t="b">
+        <v>0</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G576" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H576" t="n">
+        <v>3</v>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L576" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M576" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>(498, 19)</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>(103, 19)</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>(83, 19)</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R576" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>612</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>3</v>
+      </c>
+      <c r="D577" t="b">
+        <v>0</v>
+      </c>
+      <c r="E577" t="b">
+        <v>0</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G577" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H577" t="n">
+        <v>3</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L577" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M577" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>(1380, 19)</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>(270, 19)</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>(216, 19)</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R577" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>614</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>3</v>
+      </c>
+      <c r="D578" t="b">
+        <v>0</v>
+      </c>
+      <c r="E578" t="b">
+        <v>0</v>
+      </c>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr"/>
+      <c r="H578" t="n">
+        <v>3</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L578" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M578" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>(1470, 84)</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>(292, 84)</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>(234, 84)</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R578" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>616</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>3</v>
+      </c>
+      <c r="D579" t="b">
+        <v>0</v>
+      </c>
+      <c r="E579" t="b">
+        <v>0</v>
+      </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H579" t="n">
+        <v>3</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L579" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M579" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>(1614, 63)</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>(320, 63)</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>(256, 63)</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R579" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>617</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>3</v>
+      </c>
+      <c r="D580" t="b">
+        <v>0</v>
+      </c>
+      <c r="E580" t="b">
+        <v>0</v>
+      </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H580" t="n">
+        <v>3</v>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L580" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M580" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>(594, 42)</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>(124, 42)</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>(99, 42)</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R580" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>618</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>3</v>
+      </c>
+      <c r="D581" t="b">
+        <v>0</v>
+      </c>
+      <c r="E581" t="b">
+        <v>0</v>
+      </c>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H581" t="n">
+        <v>3</v>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L581" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M581" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>(1674, 42)</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>(329, 42)</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>(263, 42)</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R581" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>619</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>3</v>
+      </c>
+      <c r="D582" t="b">
+        <v>0</v>
+      </c>
+      <c r="E582" t="b">
+        <v>0</v>
+      </c>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H582" t="n">
+        <v>3</v>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L582" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M582" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>(891, 21)</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>(180, 21)</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>(144, 21)</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R582" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>620</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>3</v>
+      </c>
+      <c r="D583" t="b">
+        <v>0</v>
+      </c>
+      <c r="E583" t="b">
+        <v>0</v>
+      </c>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H583" t="n">
+        <v>3</v>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L583" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M583" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>(1524, 21)</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>(300, 21)</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>(240, 21)</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R583" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>621</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>3</v>
+      </c>
+      <c r="D584" t="b">
+        <v>0</v>
+      </c>
+      <c r="E584" t="b">
+        <v>0</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G584" t="inlineStr"/>
+      <c r="H584" t="n">
+        <v>5</v>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L584" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M584" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>(597, 51)</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>(131, 51)</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>(105, 51)</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R584" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>622</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>3</v>
+      </c>
+      <c r="D585" t="b">
+        <v>0</v>
+      </c>
+      <c r="E585" t="b">
+        <v>0</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G585" t="inlineStr"/>
+      <c r="H585" t="n">
+        <v>5</v>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L585" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M585" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>(2649, 51)</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>(519, 51)</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>(415, 51)</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R585" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>623</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>3</v>
+      </c>
+      <c r="D586" t="b">
+        <v>0</v>
+      </c>
+      <c r="E586" t="b">
+        <v>0</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G586" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H586" t="n">
+        <v>5</v>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L586" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M586" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>(642, 38)</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>(131, 38)</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>(105, 38)</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R586" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>624</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>3</v>
+      </c>
+      <c r="D587" t="b">
+        <v>0</v>
+      </c>
+      <c r="E587" t="b">
+        <v>0</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G587" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H587" t="n">
+        <v>5</v>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L587" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M587" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>(2571, 38)</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>(506, 38)</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>(405, 38)</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R587" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>625</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>3</v>
+      </c>
+      <c r="D588" t="b">
+        <v>0</v>
+      </c>
+      <c r="E588" t="b">
+        <v>0</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G588" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H588" t="n">
+        <v>5</v>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L588" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M588" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>(966, 26)</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>(197, 26)</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>(158, 26)</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R588" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>626</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>3</v>
+      </c>
+      <c r="D589" t="b">
+        <v>0</v>
+      </c>
+      <c r="E589" t="b">
+        <v>0</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G589" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H589" t="n">
+        <v>5</v>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L589" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M589" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>(2685, 26)</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>(522, 26)</t>
+        </is>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>(418, 26)</t>
+        </is>
+      </c>
+      <c r="Q589" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R589" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>627</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>3</v>
+      </c>
+      <c r="D590" t="b">
+        <v>0</v>
+      </c>
+      <c r="E590" t="b">
+        <v>0</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G590" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H590" t="n">
+        <v>5</v>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L590" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M590" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>(951, 13)</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>(199, 13)</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>(159, 13)</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R590" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>628</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>3</v>
+      </c>
+      <c r="D591" t="b">
+        <v>0</v>
+      </c>
+      <c r="E591" t="b">
+        <v>0</v>
+      </c>
+      <c r="F591" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G591" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H591" t="n">
+        <v>5</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L591" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M591" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>(2700, 13)</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>(527, 13)</t>
+        </is>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>(421, 13)</t>
+        </is>
+      </c>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R591" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>629</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>3</v>
+      </c>
+      <c r="D592" t="b">
+        <v>0</v>
+      </c>
+      <c r="E592" t="b">
+        <v>0</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="n">
+        <v>5</v>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L592" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M592" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>(930, 74)</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>(189, 74)</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>(151, 74)</t>
+        </is>
+      </c>
+      <c r="Q592" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R592" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>630</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>3</v>
+      </c>
+      <c r="D593" t="b">
+        <v>0</v>
+      </c>
+      <c r="E593" t="b">
+        <v>0</v>
+      </c>
+      <c r="F593" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="n">
+        <v>5</v>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L593" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M593" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>(2391, 74)</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>(465, 74)</t>
+        </is>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>(372, 74)</t>
+        </is>
+      </c>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R593" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>631</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>3</v>
+      </c>
+      <c r="D594" t="b">
+        <v>0</v>
+      </c>
+      <c r="E594" t="b">
+        <v>0</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G594" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H594" t="n">
+        <v>5</v>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L594" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M594" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>(927, 55)</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>(190, 55)</t>
+        </is>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>(152, 55)</t>
+        </is>
+      </c>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>['referee', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R594" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>632</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>3</v>
+      </c>
+      <c r="D595" t="b">
+        <v>0</v>
+      </c>
+      <c r="E595" t="b">
+        <v>0</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G595" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H595" t="n">
+        <v>5</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L595" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M595" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>(2139, 55)</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>(408, 55)</t>
+        </is>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>(326, 55)</t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t>['referee', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R595" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>633</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>3</v>
+      </c>
+      <c r="D596" t="b">
+        <v>0</v>
+      </c>
+      <c r="E596" t="b">
+        <v>0</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G596" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H596" t="n">
+        <v>5</v>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L596" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M596" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>(951, 37)</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>(190, 37)</t>
+        </is>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>(152, 37)</t>
+        </is>
+      </c>
+      <c r="Q596" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R596" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>634</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>3</v>
+      </c>
+      <c r="D597" t="b">
+        <v>0</v>
+      </c>
+      <c r="E597" t="b">
+        <v>0</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G597" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H597" t="n">
+        <v>5</v>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L597" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M597" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>(1680, 37)</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>(329, 37)</t>
+        </is>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>(263, 37)</t>
+        </is>
+      </c>
+      <c r="Q597" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R597" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>635</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>3</v>
+      </c>
+      <c r="D598" t="b">
+        <v>0</v>
+      </c>
+      <c r="E598" t="b">
+        <v>0</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G598" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H598" t="n">
+        <v>5</v>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L598" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M598" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>(1314, 19)</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>(266, 19)</t>
+        </is>
+      </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>(213, 19)</t>
+        </is>
+      </c>
+      <c r="Q598" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R598" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>636</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>3</v>
+      </c>
+      <c r="D599" t="b">
+        <v>0</v>
+      </c>
+      <c r="E599" t="b">
+        <v>0</v>
+      </c>
+      <c r="F599" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G599" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H599" t="n">
+        <v>5</v>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L599" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M599" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>(2718, 19)</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>(527, 19)</t>
+        </is>
+      </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>(421, 19)</t>
+        </is>
+      </c>
+      <c r="Q599" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R599" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>638</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>3</v>
+      </c>
+      <c r="D600" t="b">
+        <v>0</v>
+      </c>
+      <c r="E600" t="b">
+        <v>0</v>
+      </c>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr"/>
+      <c r="H600" t="n">
+        <v>5</v>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L600" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M600" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>(2409, 84)</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>(465, 84)</t>
+        </is>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>(372, 84)</t>
+        </is>
+      </c>
+      <c r="Q600" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_60_matches_PPDA', 'dif_mean_last_60_matches_PPDA_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R600" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>640</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>3</v>
+      </c>
+      <c r="D601" t="b">
+        <v>0</v>
+      </c>
+      <c r="E601" t="b">
+        <v>0</v>
+      </c>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H601" t="n">
+        <v>5</v>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L601" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M601" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>(2574, 63)</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>(511, 63)</t>
+        </is>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>(409, 63)</t>
+        </is>
+      </c>
+      <c r="Q601" t="inlineStr">
+        <is>
+          <t>['referee', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_60_matches_PPS', 'dif_mean_last_60_matches_PPS_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R601" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>641</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>3</v>
+      </c>
+      <c r="D602" t="b">
+        <v>0</v>
+      </c>
+      <c r="E602" t="b">
+        <v>0</v>
+      </c>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H602" t="n">
+        <v>5</v>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L602" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M602" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>(897, 42)</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>(185, 42)</t>
+        </is>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>(148, 42)</t>
+        </is>
+      </c>
+      <c r="Q602" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R602" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>642</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>3</v>
+      </c>
+      <c r="D603" t="b">
+        <v>0</v>
+      </c>
+      <c r="E603" t="b">
+        <v>0</v>
+      </c>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H603" t="n">
+        <v>5</v>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L603" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M603" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>(2067, 42)</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>(410, 42)</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>(328, 42)</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_60_matches_total_passes_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R603" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>643</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>3</v>
+      </c>
+      <c r="D604" t="b">
+        <v>0</v>
+      </c>
+      <c r="E604" t="b">
+        <v>0</v>
+      </c>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H604" t="n">
+        <v>5</v>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L604" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M604" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>(1308, 21)</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>(266, 21)</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>(213, 21)</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R604" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>644</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>3</v>
+      </c>
+      <c r="D605" t="b">
+        <v>0</v>
+      </c>
+      <c r="E605" t="b">
+        <v>0</v>
+      </c>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H605" t="n">
+        <v>5</v>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L605" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M605" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>(2436, 21)</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>(479, 21)</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>(383, 21)</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_total_passes', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R605" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>645</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>3</v>
+      </c>
+      <c r="D606" t="b">
+        <v>0</v>
+      </c>
+      <c r="E606" t="b">
+        <v>0</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G606" t="inlineStr"/>
+      <c r="H606" t="n">
+        <v>10</v>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L606" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M606" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>(834, 49)</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>(174, 49)</t>
+        </is>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>(139, 49)</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R606" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>646</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>3</v>
+      </c>
+      <c r="D607" t="b">
+        <v>0</v>
+      </c>
+      <c r="E607" t="b">
+        <v>0</v>
+      </c>
+      <c r="F607" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G607" t="inlineStr"/>
+      <c r="H607" t="n">
+        <v>10</v>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L607" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M607" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>(2136, 49)</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>(427, 49)</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>(341, 49)</t>
+        </is>
+      </c>
+      <c r="Q607" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R607" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>647</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>3</v>
+      </c>
+      <c r="D608" t="b">
+        <v>0</v>
+      </c>
+      <c r="E608" t="b">
+        <v>0</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G608" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H608" t="n">
+        <v>10</v>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L608" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M608" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>(864, 37)</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>(174, 37)</t>
+        </is>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>(139, 37)</t>
+        </is>
+      </c>
+      <c r="Q608" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R608" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>648</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>3</v>
+      </c>
+      <c r="D609" t="b">
+        <v>0</v>
+      </c>
+      <c r="E609" t="b">
+        <v>0</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G609" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H609" t="n">
+        <v>10</v>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L609" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M609" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>(2265, 37)</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>(437, 37)</t>
+        </is>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>(350, 37)</t>
+        </is>
+      </c>
+      <c r="Q609" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R609" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>649</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>3</v>
+      </c>
+      <c r="D610" t="b">
+        <v>0</v>
+      </c>
+      <c r="E610" t="b">
+        <v>0</v>
+      </c>
+      <c r="F610" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G610" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H610" t="n">
+        <v>10</v>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L610" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M610" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>(1293, 25)</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>(249, 25)</t>
+        </is>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>(200, 25)</t>
+        </is>
+      </c>
+      <c r="Q610" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R610" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>650</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>3</v>
+      </c>
+      <c r="D611" t="b">
+        <v>0</v>
+      </c>
+      <c r="E611" t="b">
+        <v>0</v>
+      </c>
+      <c r="F611" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G611" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H611" t="n">
+        <v>10</v>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L611" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M611" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>(2325, 25)</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>(453, 25)</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>(362, 25)</t>
+        </is>
+      </c>
+      <c r="Q611" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub']</t>
+        </is>
+      </c>
+      <c r="R611" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>651</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>3</v>
+      </c>
+      <c r="D612" t="b">
+        <v>0</v>
+      </c>
+      <c r="E612" t="b">
+        <v>0</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G612" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H612" t="n">
+        <v>10</v>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L612" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M612" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>(1833, 13)</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>(358, 13)</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>(286, 13)</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub']</t>
+        </is>
+      </c>
+      <c r="R612" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>652</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>3</v>
+      </c>
+      <c r="D613" t="b">
+        <v>0</v>
+      </c>
+      <c r="E613" t="b">
+        <v>0</v>
+      </c>
+      <c r="F613" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G613" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H613" t="n">
+        <v>10</v>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L613" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M613" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>(3294, 13)</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>(653, 13)</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>(522, 13)</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub']</t>
+        </is>
+      </c>
+      <c r="R613" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>653</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>3</v>
+      </c>
+      <c r="D614" t="b">
+        <v>0</v>
+      </c>
+      <c r="E614" t="b">
+        <v>0</v>
+      </c>
+      <c r="F614" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G614" t="inlineStr"/>
+      <c r="H614" t="n">
+        <v>10</v>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L614" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M614" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>(852, 71)</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>(173, 71)</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>(139, 71)</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R614" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>654</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>3</v>
+      </c>
+      <c r="D615" t="b">
+        <v>0</v>
+      </c>
+      <c r="E615" t="b">
+        <v>0</v>
+      </c>
+      <c r="F615" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G615" t="inlineStr"/>
+      <c r="H615" t="n">
+        <v>10</v>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L615" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M615" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>(2148, 71)</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>(435, 71)</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>(348, 71)</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R615" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>655</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>3</v>
+      </c>
+      <c r="D616" t="b">
+        <v>0</v>
+      </c>
+      <c r="E616" t="b">
+        <v>0</v>
+      </c>
+      <c r="F616" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G616" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H616" t="n">
+        <v>10</v>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L616" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M616" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>(870, 53)</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>(174, 53)</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>(140, 53)</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R616" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>656</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>3</v>
+      </c>
+      <c r="D617" t="b">
+        <v>0</v>
+      </c>
+      <c r="E617" t="b">
+        <v>0</v>
+      </c>
+      <c r="F617" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G617" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H617" t="n">
+        <v>10</v>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L617" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M617" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>(2214, 53)</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>(438, 53)</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>(350, 53)</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R617" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>657</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>3</v>
+      </c>
+      <c r="D618" t="b">
+        <v>0</v>
+      </c>
+      <c r="E618" t="b">
+        <v>0</v>
+      </c>
+      <c r="F618" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G618" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H618" t="n">
+        <v>10</v>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L618" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M618" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>(1284, 36)</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>(252, 36)</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>(202, 36)</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R618" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>658</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>3</v>
+      </c>
+      <c r="D619" t="b">
+        <v>0</v>
+      </c>
+      <c r="E619" t="b">
+        <v>0</v>
+      </c>
+      <c r="F619" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G619" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H619" t="n">
+        <v>10</v>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L619" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M619" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>(3288, 36)</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>(651, 36)</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>(520, 36)</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R619" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>659</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>3</v>
+      </c>
+      <c r="D620" t="b">
+        <v>0</v>
+      </c>
+      <c r="E620" t="b">
+        <v>0</v>
+      </c>
+      <c r="F620" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G620" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H620" t="n">
+        <v>10</v>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L620" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M620" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>(1836, 18)</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>(357, 18)</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>(285, 18)</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R620" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>660</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>3</v>
+      </c>
+      <c r="D621" t="b">
+        <v>0</v>
+      </c>
+      <c r="E621" t="b">
+        <v>0</v>
+      </c>
+      <c r="F621" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G621" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H621" t="n">
+        <v>10</v>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L621" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M621" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>(3330, 18)</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>(653, 18)</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>(522, 18)</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R621" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>661</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>3</v>
+      </c>
+      <c r="D622" t="b">
+        <v>0</v>
+      </c>
+      <c r="E622" t="b">
+        <v>0</v>
+      </c>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="inlineStr"/>
+      <c r="H622" t="n">
+        <v>10</v>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L622" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M622" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>(867, 78)</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>(173, 78)</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>(139, 78)</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R622" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>662</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>3</v>
+      </c>
+      <c r="D623" t="b">
+        <v>0</v>
+      </c>
+      <c r="E623" t="b">
+        <v>0</v>
+      </c>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="inlineStr"/>
+      <c r="H623" t="n">
+        <v>10</v>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L623" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M623" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>(2148, 78)</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>(435, 78)</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>(348, 78)</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>['referee', 'id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_expected_points_against', 'dif_mean_last_240_matches_expected_points', 'dif_mean_last_240_matches_expected_points_against', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_60_matches_shots_on_goal_against', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio_against', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_PPS_against', 'dif_mean_last_60_matches_attacks', 'dif_mean_last_60_matches_attacks_against', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_60_matches_dangerous_attacks_against', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_240_matches_yellow_cards_against', 'dif_mean_last_60_matches_red_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_240_matches_red_cards', 'dif_mean_last_240_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_age_player_sub', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_hei_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R623" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>663</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>3</v>
+      </c>
+      <c r="D624" t="b">
+        <v>0</v>
+      </c>
+      <c r="E624" t="b">
+        <v>0</v>
+      </c>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H624" t="n">
+        <v>10</v>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L624" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M624" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>(852, 58)</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>(174, 58)</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>(139, 58)</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R624" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>664</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>3</v>
+      </c>
+      <c r="D625" t="b">
+        <v>0</v>
+      </c>
+      <c r="E625" t="b">
+        <v>0</v>
+      </c>
+      <c r="F625" t="inlineStr"/>
+      <c r="G625" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H625" t="n">
+        <v>10</v>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L625" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M625" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>(2196, 58)</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>(438, 58)</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>(350, 58)</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>['id_coach_home', 'id_coach_away', 'is_cup', 'dif_mean_last_60_matches_expected_points', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_60_matches_goal_ratio_against', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_240_matches_attacks_against', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_60_matches_dead_balls_against', 'dif_mean_last_240_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_240_matches_total_passes', 'dif_mean_last_240_matches_total_passes_against', 'dif_mean_last_60_matches_yellow_cards_against', 'dif_mean_last_240_matches_yellow_cards', 'dif_mean_last_60_matches_red_cards_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_KGP', 'dif_mean_last_240_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R625" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>665</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>3</v>
+      </c>
+      <c r="D626" t="b">
+        <v>0</v>
+      </c>
+      <c r="E626" t="b">
+        <v>0</v>
+      </c>
+      <c r="F626" t="inlineStr"/>
+      <c r="G626" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H626" t="n">
+        <v>10</v>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L626" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M626" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>(1221, 39)</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>(252, 39)</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>(202, 39)</t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R626" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>666</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>3</v>
+      </c>
+      <c r="D627" t="b">
+        <v>0</v>
+      </c>
+      <c r="E627" t="b">
+        <v>0</v>
+      </c>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H627" t="n">
+        <v>10</v>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L627" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M627" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>(3288, 39)</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>(651, 39)</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>(520, 39)</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal_against', 'dif_mean_last_60_matches_goal_attempts', 'dif_mean_last_60_matches_goal_attempts_against', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_240_matches_goal_attempts_against', 'dif_mean_last_60_matches_goals', 'dif_mean_last_60_matches_goals_against', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_60_matches_points', 'dif_mean_last_60_matches_points_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_goal_ratio', 'dif_mean_last_240_matches_PPS', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_dead_balls', 'dif_mean_last_240_matches_dead_balls_against', 'dif_mean_last_60_matches_ball_possession_against', 'dif_mean_last_240_matches_ball_possession_against', 'dif_mean_last_60_matches_defensive_actions', 'dif_mean_last_60_matches_defensive_actions_against', 'dif_mean_last_240_matches_PPDA_against', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_60_matches_clean_sheet_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rep_player_sub', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_wage_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R627" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>667</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>3</v>
+      </c>
+      <c r="D628" t="b">
+        <v>0</v>
+      </c>
+      <c r="E628" t="b">
+        <v>0</v>
+      </c>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H628" t="n">
+        <v>10</v>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L628" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M628" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>(2271, 20)</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>(457, 20)</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>(366, 20)</t>
+        </is>
+      </c>
+      <c r="Q628" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R628" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>668</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>[60, 240]</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>3</v>
+      </c>
+      <c r="D629" t="b">
+        <v>0</v>
+      </c>
+      <c r="E629" t="b">
+        <v>0</v>
+      </c>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H629" t="n">
+        <v>10</v>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>[1481, 1482, 1483, 1484]</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="L629" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M629" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>(3336, 20)</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>(653, 20)</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>(522, 20)</t>
+        </is>
+      </c>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>['is_cup', 'dif_mean_last_60_matches_shots_on_goal', 'dif_mean_last_240_matches_shots_on_goal', 'dif_mean_last_240_matches_goal_attempts', 'dif_mean_last_60_matches_goals', 'dif_mean_last_240_matches_goals', 'dif_mean_last_240_matches_goals_against', 'dif_mean_last_240_matches_points', 'dif_mean_last_240_matches_points_against', 'dif_mean_last_60_matches_goal_ratio', 'dif_mean_last_240_matches_attacks', 'dif_mean_last_60_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks', 'dif_mean_last_240_matches_dangerous_attacks_against', 'dif_mean_last_60_matches_KGP_against', 'dif_mean_last_240_matches_clean_sheet_against', 'dif_mean_last_240_matches_mean_rat_player_start_against', 'dif_mean_rat_player_sub', 'dif_mean_pot_player_sub', 'dif_mean_value_player_sub']</t>
+        </is>
+      </c>
+      <c r="R629" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
